--- a/erp-server/erp-server-file/src/main/resources/excel/wms/virtualAdjustExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/virtualAdjustExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>单据单号</t>
   </si>
@@ -58,6 +58,9 @@
     <t>备注</t>
   </si>
   <si>
+    <t>明细备注</t>
+  </si>
+  <si>
     <t>创建人</t>
   </si>
   <si>
@@ -95,6 +98,9 @@
   </si>
   <si>
     <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.detailRemark}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1070,7 +1076,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.75" customWidth="1"/>
@@ -1082,13 +1088,14 @@
     <col min="7" max="7" width="15.875" customWidth="1"/>
     <col min="8" max="8" width="15.25" customWidth="1"/>
     <col min="9" max="9" width="17.75" customWidth="1"/>
-    <col min="10" max="10" width="13.5" customWidth="1"/>
-    <col min="11" max="11" width="11.875" customWidth="1"/>
-    <col min="12" max="12" width="15.25" customWidth="1"/>
-    <col min="13" max="13" width="13.375" customWidth="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="11.875" customWidth="1"/>
+    <col min="13" max="13" width="15.25" customWidth="1"/>
+    <col min="14" max="14" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:13">
+    <row r="1" customFormat="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1128,46 +1135,52 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/virtualAdjustExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/virtualAdjustExport.xlsx
@@ -91,7 +91,7 @@
     <t>{.virtualWarehouseName}</t>
   </si>
   <si>
-    <t>{.dictInventoryStatusName}</t>
+    <t>{.inventoryStatusName}</t>
   </si>
   <si>
     <t>{.qty}</t>
